--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,14 +751,14 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F12" t="n">
-        <v>150218.4</v>
+        <v>181810.83</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 400股</t>
+          <t>；仍卖出未平仓 500股</t>
         </is>
       </c>
     </row>
@@ -1156,14 +1156,14 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F27" t="n">
-        <v>36706</v>
+        <v>55059</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 400股</t>
+          <t>；仍卖出未平仓 600股</t>
         </is>
       </c>
     </row>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="D31" t="n">
-        <v>155160.8</v>
+        <v>114123.66</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>仍买入未平仓 700股</t>
+          <t>仍买入未平仓 500股</t>
         </is>
       </c>
     </row>
@@ -1407,6 +1407,33 @@
       <c r="G36" t="inlineStr">
         <is>
           <t>仅买入未平仓 70000股（跨年持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>603228</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>景旺电子</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>300</v>
+      </c>
+      <c r="D37" t="n">
+        <v>31566</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 300股（跨年持有底仓）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="D31" t="n">
-        <v>114123.66</v>
+        <v>155211.41</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>仍买入未平仓 500股</t>
+          <t>仍买入未平仓 700股</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,14 +562,14 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="F5" t="n">
-        <v>58982.58</v>
+        <v>79316.81</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 1500股</t>
+          <t>；仍卖出未平仓 2000股</t>
         </is>
       </c>
     </row>
@@ -994,14 +994,14 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="F21" t="n">
-        <v>189680.31</v>
+        <v>126453.54</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 600股</t>
+          <t>；仍卖出未平仓 400股</t>
         </is>
       </c>
     </row>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="D31" t="n">
-        <v>155211.41</v>
+        <v>114123.66</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>仍买入未平仓 700股</t>
+          <t>仍买入未平仓 500股</t>
         </is>
       </c>
     </row>
@@ -1412,26 +1412,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
+        <v>2916</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>深南电路</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>100</v>
+      </c>
+      <c r="D37" t="n">
+        <v>38629</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 100股（跨年持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
         <v>603228</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>景旺电子</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C38" t="n">
         <v>300</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D38" t="n">
         <v>31566</v>
       </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>仅买入未平仓 300股（跨年持有底仓）</t>
         </is>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -466,8 +466,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>831</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -493,8 +495,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2156</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -520,8 +524,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2384</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -547,8 +553,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2436</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -574,8 +582,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2837</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -601,8 +611,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>123269</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>123269</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -628,8 +640,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>300394</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -655,8 +669,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>300450</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>300450</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -682,8 +698,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>300502</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -700,7 +718,7 @@
         <v>540</v>
       </c>
       <c r="F10" t="n">
-        <v>287104.93</v>
+        <v>287104.92</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -709,8 +727,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>300660</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>300660</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -736,8 +756,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>300750</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -763,8 +785,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>512000</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>512000</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -790,8 +814,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>600259</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>600259</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -817,8 +843,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>600498</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -844,8 +872,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>601208</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -871,8 +901,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>601899</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -898,8 +930,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>603881</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>603881</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -925,8 +959,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>688025</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -952,8 +988,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>688035</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>688035</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -964,7 +1002,7 @@
         <v>400</v>
       </c>
       <c r="D20" t="n">
-        <v>35694.66</v>
+        <v>35694.67</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -979,8 +1017,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>688041</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1006,8 +1046,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>688062</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>688062</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1033,8 +1075,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>21</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>000021</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1060,8 +1104,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>988</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1087,8 +1133,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>2222</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1114,8 +1162,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>2594</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1141,8 +1191,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>300054</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1168,8 +1220,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>300274</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>300274</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1195,8 +1249,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>300308</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1222,8 +1278,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>300548</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1249,8 +1307,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>688008</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1276,8 +1336,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>688676</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>688676</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1303,8 +1365,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>688778</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>688778</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1330,8 +1394,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>603920</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>603920</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1357,8 +1423,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>512760</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>512760</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1384,8 +1452,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>561980</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1411,8 +1481,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>2916</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>002916</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1438,8 +1510,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>603228</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>603228</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,14 +570,14 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="F5" t="n">
-        <v>79316.81</v>
+        <v>100566.64</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 2000股</t>
+          <t>；仍卖出未平仓 2500股</t>
         </is>
       </c>
     </row>
@@ -773,14 +773,14 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F12" t="n">
-        <v>181810.83</v>
+        <v>150218.4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 500股</t>
+          <t>；仍卖出未平仓 400股</t>
         </is>
       </c>
     </row>
@@ -1034,14 +1034,14 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F21" t="n">
-        <v>126453.54</v>
+        <v>189680.31</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 400股</t>
+          <t>；仍卖出未平仓 600股</t>
         </is>
       </c>
     </row>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="D31" t="n">
-        <v>114123.66</v>
+        <v>68474.19</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>仍买入未平仓 500股</t>
+          <t>仍买入未平仓 300股</t>
         </is>
       </c>
     </row>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>70000</v>
+        <v>60000</v>
       </c>
       <c r="D36" t="n">
-        <v>48633.24</v>
+        <v>41975.24</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>仅买入未平仓 70000股（跨年持有底仓）</t>
+          <t>仅买入未平仓 60000股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -1535,6 +1535,35 @@
       <c r="G38" t="inlineStr">
         <is>
           <t>仅买入未平仓 300股（跨年持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>688820</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>盛合晶微</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>200</v>
+      </c>
+      <c r="D39" t="n">
+        <v>28090</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 200股（跨年持有底仓）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,14 +570,14 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="F5" t="n">
-        <v>100566.64</v>
+        <v>92272.02</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 2500股</t>
+          <t>；仍卖出未平仓 2300股</t>
         </is>
       </c>
     </row>
@@ -773,14 +773,14 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F12" t="n">
-        <v>150218.4</v>
+        <v>181752.5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 400股</t>
+          <t>；仍卖出未平仓 500股</t>
         </is>
       </c>
     </row>
@@ -1063,14 +1063,14 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="F22" t="n">
-        <v>127885</v>
+        <v>141770</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 4000股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 4500股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>60000</v>
+        <v>70000</v>
       </c>
       <c r="D36" t="n">
-        <v>41975.24</v>
+        <v>48821.24</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>仅买入未平仓 60000股（跨年持有底仓）</t>
+          <t>仅买入未平仓 70000股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -1512,19 +1512,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>603228</t>
+          <t>600127</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>景旺电子</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="D38" t="n">
-        <v>31566</v>
+        <v>8015</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -1534,36 +1534,123 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>仅买入未平仓 300股（跨年持有底仓）</t>
+          <t>仅买入未平仓 500股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>603228</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>景旺电子</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>400</v>
+      </c>
+      <c r="D39" t="n">
+        <v>42366</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 400股（跨年持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>688127</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>蓝特光学</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>200</v>
+      </c>
+      <c r="D40" t="n">
+        <v>13902</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 200股（跨年持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>688603</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>天承科技</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>161</v>
+      </c>
+      <c r="D41" t="n">
+        <v>19704.79</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 161股（跨年持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>688820</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>盛合晶微</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>200</v>
-      </c>
-      <c r="D39" t="n">
-        <v>28090</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>仅买入未平仓 200股（跨年持有底仓）</t>
+      <c r="C42" t="n">
+        <v>400</v>
+      </c>
+      <c r="D42" t="n">
+        <v>55930</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 400股（跨年持有底仓）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,14 +570,14 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2300</v>
+        <v>2500</v>
       </c>
       <c r="F5" t="n">
-        <v>92272.02</v>
+        <v>100971.07</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 2300股</t>
+          <t>；仍卖出未平仓 2500股</t>
         </is>
       </c>
     </row>
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="D6" t="n">
-        <v>32315</v>
+        <v>50781.33</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -606,7 +606,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>仍买入未平仓 500股</t>
+          <t>仍买入未平仓 800股</t>
         </is>
       </c>
     </row>
@@ -773,14 +773,14 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F12" t="n">
-        <v>181752.5</v>
+        <v>212748.28</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 500股</t>
+          <t>；仍卖出未平仓 600股</t>
         </is>
       </c>
     </row>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="D25" t="n">
-        <v>24416.86</v>
+        <v>44436.98</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>仍买入未平仓 400股</t>
+          <t>仍买入未平仓 700股</t>
         </is>
       </c>
     </row>
@@ -1512,19 +1512,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>600127</t>
+          <t>603228</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>景旺电子</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="D38" t="n">
-        <v>8015</v>
+        <v>64186</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -1534,26 +1534,26 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>仅买入未平仓 500股（跨年持有底仓）</t>
+          <t>仅买入未平仓 600股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>603228</t>
+          <t>688127</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>景旺电子</t>
+          <t>蓝特光学</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="D39" t="n">
-        <v>42366</v>
+        <v>13902</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -1563,26 +1563,26 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>仅买入未平仓 400股（跨年持有底仓）</t>
+          <t>仅买入未平仓 200股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>688127</t>
+          <t>688603</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>蓝特光学</t>
+          <t>天承科技</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D40" t="n">
-        <v>13902</v>
+        <v>12239</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -1592,26 +1592,26 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨年持有底仓）</t>
+          <t>仅买入未平仓 100股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>688603</t>
+          <t>688820</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>天承科技</t>
+          <t>盛合晶微</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>161</v>
+        <v>400</v>
       </c>
       <c r="D41" t="n">
-        <v>19704.79</v>
+        <v>55930</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -1620,35 +1620,6 @@
         <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
-        <is>
-          <t>仅买入未平仓 161股（跨年持有底仓）</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>688820</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>盛合晶微</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>400</v>
-      </c>
-      <c r="D42" t="n">
-        <v>55930</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="inlineStr">
         <is>
           <t>仅买入未平仓 400股（跨年持有底仓）</t>
         </is>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -570,14 +570,14 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="F5" t="n">
-        <v>100971.07</v>
+        <v>80063.88</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 2500股</t>
+          <t>；仍卖出未平仓 2000股</t>
         </is>
       </c>
     </row>
@@ -1034,14 +1034,14 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="F21" t="n">
-        <v>189680.31</v>
+        <v>126453.54</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 600股</t>
+          <t>；仍卖出未平仓 400股</t>
         </is>
       </c>
     </row>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="D39" t="n">
-        <v>13902</v>
+        <v>40542</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨年持有底仓）</t>
+          <t>仅买入未平仓 600股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D40" t="n">
-        <v>12239</v>
+        <v>24756.16</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>仅买入未平仓 100股（跨年持有底仓）</t>
+          <t>仅买入未平仓 200股（跨年持有底仓）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="D39" t="n">
-        <v>40542</v>
+        <v>53122</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>仅买入未平仓 600股（跨年持有底仓）</t>
+          <t>仅买入未平仓 800股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D40" t="n">
-        <v>24756.16</v>
+        <v>48339.08</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨年持有底仓）</t>
+          <t>仅买入未平仓 400股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
